--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123321603</v>
       </c>
       <c r="B2" t="n">
-        <v>98282</v>
+        <v>98285</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321599</v>
+        <v>123321598</v>
       </c>
       <c r="B3" t="n">
-        <v>56680</v>
+        <v>56694</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,20 +822,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614390</v>
+        <v>614543</v>
       </c>
       <c r="R3" t="n">
-        <v>6942878</v>
+        <v>6942796</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_348</t>
+          <t>2024_349</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>spillning i myrkant.</t>
+          <t>orrspillning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -948,7 +948,7 @@
         <v>123321602</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321598</v>
+        <v>123321599</v>
       </c>
       <c r="B5" t="n">
-        <v>56691</v>
+        <v>56683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,20 +1092,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614543</v>
+        <v>614390</v>
       </c>
       <c r="R5" t="n">
-        <v>6942796</v>
+        <v>6942878</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_349</t>
+          <t>2024_348</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>orrspillning.</t>
+          <t>spillning i myrkant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321603</v>
+        <v>123321602</v>
       </c>
       <c r="B2" t="n">
-        <v>98285</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614270</v>
+        <v>614303</v>
       </c>
       <c r="R2" t="n">
-        <v>6942929</v>
+        <v>6942906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_344</t>
+          <t>2024_345</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på myr</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321602</v>
+        <v>123321603</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>98287</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,35 +957,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614303</v>
+        <v>614270</v>
       </c>
       <c r="R4" t="n">
-        <v>6942906</v>
+        <v>6942929</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_345</t>
+          <t>2024_344</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>på myr</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Felix Gunnarsson, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321602</v>
+        <v>123321603</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>98293</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614303</v>
+        <v>614270</v>
       </c>
       <c r="R2" t="n">
-        <v>6942906</v>
+        <v>6942929</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_345</t>
+          <t>2024_344</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>på myr</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Felix Gunnarsson, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321598</v>
+        <v>123321602</v>
       </c>
       <c r="B3" t="n">
-        <v>56694</v>
+        <v>78772</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614543</v>
+        <v>614303</v>
       </c>
       <c r="R3" t="n">
-        <v>6942796</v>
+        <v>6942906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_349</t>
+          <t>2024_345</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>orrspillning.</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321603</v>
+        <v>123321599</v>
       </c>
       <c r="B4" t="n">
-        <v>98287</v>
+        <v>56683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,25 +957,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -983,9 +983,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614270</v>
+        <v>614390</v>
       </c>
       <c r="R4" t="n">
-        <v>6942929</v>
+        <v>6942878</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_344</t>
+          <t>2024_348</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på myr</t>
+          <t>spillning i myrkant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Douglas Skarp</t>
+          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321599</v>
+        <v>123321598</v>
       </c>
       <c r="B5" t="n">
-        <v>56683</v>
+        <v>56694</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,20 +1092,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614390</v>
+        <v>614543</v>
       </c>
       <c r="R5" t="n">
-        <v>6942878</v>
+        <v>6942796</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_348</t>
+          <t>2024_349</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>spillning i myrkant.</t>
+          <t>orrspillning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321603</v>
+        <v>123321599</v>
       </c>
       <c r="B2" t="n">
-        <v>98293</v>
+        <v>56683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614270</v>
+        <v>614390</v>
       </c>
       <c r="R2" t="n">
-        <v>6942929</v>
+        <v>6942878</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_344</t>
+          <t>2024_348</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på myr</t>
+          <t>spillning i myrkant.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Douglas Skarp</t>
+          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321602</v>
+        <v>123321603</v>
       </c>
       <c r="B3" t="n">
-        <v>78772</v>
+        <v>98296</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614303</v>
+        <v>614270</v>
       </c>
       <c r="R3" t="n">
-        <v>6942906</v>
+        <v>6942929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_345</t>
+          <t>2024_344</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>på myr</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Felix Gunnarsson, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321599</v>
+        <v>123321598</v>
       </c>
       <c r="B4" t="n">
-        <v>56683</v>
+        <v>56694</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,20 +957,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614390</v>
+        <v>614543</v>
       </c>
       <c r="R4" t="n">
-        <v>6942878</v>
+        <v>6942796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_348</t>
+          <t>2024_349</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>spillning i myrkant.</t>
+          <t>orrspillning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321598</v>
+        <v>123321602</v>
       </c>
       <c r="B5" t="n">
-        <v>56694</v>
+        <v>78775</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,35 +1092,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614543</v>
+        <v>614303</v>
       </c>
       <c r="R5" t="n">
-        <v>6942796</v>
+        <v>6942906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_349</t>
+          <t>2024_345</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>orrspillning.</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123321599</v>
       </c>
       <c r="B2" t="n">
-        <v>56683</v>
+        <v>56689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321603</v>
+        <v>123321602</v>
       </c>
       <c r="B3" t="n">
-        <v>98296</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614270</v>
+        <v>614303</v>
       </c>
       <c r="R3" t="n">
-        <v>6942929</v>
+        <v>6942906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_344</t>
+          <t>2024_345</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på myr</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -948,7 +948,7 @@
         <v>123321598</v>
       </c>
       <c r="B4" t="n">
-        <v>56694</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321602</v>
+        <v>123321603</v>
       </c>
       <c r="B5" t="n">
-        <v>78775</v>
+        <v>98313</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,35 +1092,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614303</v>
+        <v>614270</v>
       </c>
       <c r="R5" t="n">
-        <v>6942906</v>
+        <v>6942929</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_345</t>
+          <t>2024_344</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>på myr</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Felix Gunnarsson, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321599</v>
+        <v>123321598</v>
       </c>
       <c r="B2" t="n">
-        <v>56689</v>
+        <v>56703</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614390</v>
+        <v>614543</v>
       </c>
       <c r="R2" t="n">
-        <v>6942878</v>
+        <v>6942796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_348</t>
+          <t>2024_349</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>spillning i myrkant.</t>
+          <t>orrspillning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321602</v>
+        <v>123321599</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>56692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,31 +826,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614303</v>
+        <v>614390</v>
       </c>
       <c r="R3" t="n">
-        <v>6942906</v>
+        <v>6942878</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_345</t>
+          <t>2024_348</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>spillning i myrkant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321598</v>
+        <v>123321603</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>98419</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,21 +961,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -983,9 +983,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614543</v>
+        <v>614270</v>
       </c>
       <c r="R4" t="n">
-        <v>6942796</v>
+        <v>6942929</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_349</t>
+          <t>2024_344</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>orrspillning.</t>
+          <t>på myr</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Felix Gunnarsson, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321603</v>
+        <v>123321602</v>
       </c>
       <c r="B5" t="n">
-        <v>98313</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,35 +1092,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614270</v>
+        <v>614303</v>
       </c>
       <c r="R5" t="n">
-        <v>6942929</v>
+        <v>6942906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_344</t>
+          <t>2024_345</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på myr</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321598</v>
+        <v>123321602</v>
       </c>
       <c r="B2" t="n">
-        <v>56703</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614543</v>
+        <v>614303</v>
       </c>
       <c r="R2" t="n">
-        <v>6942796</v>
+        <v>6942906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_349</t>
+          <t>2024_345</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>orrspillning.</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321599</v>
+        <v>123321598</v>
       </c>
       <c r="B3" t="n">
-        <v>56692</v>
+        <v>56703</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,20 +822,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614390</v>
+        <v>614543</v>
       </c>
       <c r="R3" t="n">
-        <v>6942878</v>
+        <v>6942796</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_348</t>
+          <t>2024_349</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>spillning i myrkant.</t>
+          <t>orrspillning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -948,7 +948,7 @@
         <v>123321603</v>
       </c>
       <c r="B4" t="n">
-        <v>98419</v>
+        <v>98421</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321602</v>
+        <v>123321599</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>56692</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,31 +1096,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614303</v>
+        <v>614390</v>
       </c>
       <c r="R5" t="n">
-        <v>6942906</v>
+        <v>6942878</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_345</t>
+          <t>2024_348</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>spillning i myrkant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321598</v>
+        <v>123321603</v>
       </c>
       <c r="B3" t="n">
-        <v>56703</v>
+        <v>98421</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,21 +826,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,9 +848,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614543</v>
+        <v>614270</v>
       </c>
       <c r="R3" t="n">
-        <v>6942796</v>
+        <v>6942929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_349</t>
+          <t>2024_344</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>orrspillning.</t>
+          <t>på myr</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Felix Gunnarsson, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321603</v>
+        <v>123321598</v>
       </c>
       <c r="B4" t="n">
-        <v>98421</v>
+        <v>56703</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -961,21 +961,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -983,9 +983,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614270</v>
+        <v>614543</v>
       </c>
       <c r="R4" t="n">
-        <v>6942929</v>
+        <v>6942796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_344</t>
+          <t>2024_349</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på myr</t>
+          <t>orrspillning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Douglas Skarp</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321602</v>
+        <v>123321603</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>97996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614303</v>
+        <v>614270</v>
       </c>
       <c r="R2" t="n">
-        <v>6942906</v>
+        <v>6942929</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_345</t>
+          <t>2024_344</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>på myr</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Felix Gunnarsson, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321603</v>
+        <v>123321602</v>
       </c>
       <c r="B3" t="n">
-        <v>98421</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614270</v>
+        <v>614303</v>
       </c>
       <c r="R3" t="n">
-        <v>6942929</v>
+        <v>6942906</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_344</t>
+          <t>2024_345</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på myr</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321598</v>
+        <v>123321599</v>
       </c>
       <c r="B4" t="n">
-        <v>56703</v>
+        <v>56692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,20 +957,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614543</v>
+        <v>614390</v>
       </c>
       <c r="R4" t="n">
-        <v>6942796</v>
+        <v>6942878</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_349</t>
+          <t>2024_348</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>orrspillning.</t>
+          <t>spillning i myrkant.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321599</v>
+        <v>123321598</v>
       </c>
       <c r="B5" t="n">
-        <v>56692</v>
+        <v>56703</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,20 +1092,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614390</v>
+        <v>614543</v>
       </c>
       <c r="R5" t="n">
-        <v>6942878</v>
+        <v>6942796</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_348</t>
+          <t>2024_349</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>spillning i myrkant.</t>
+          <t>orrspillning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321603</v>
+        <v>123321599</v>
       </c>
       <c r="B2" t="n">
-        <v>97996</v>
+        <v>56692</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614270</v>
+        <v>614390</v>
       </c>
       <c r="R2" t="n">
-        <v>6942929</v>
+        <v>6942878</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_344</t>
+          <t>2024_348</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på myr</t>
+          <t>spillning i myrkant.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Douglas Skarp</t>
+          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321599</v>
+        <v>123321598</v>
       </c>
       <c r="B4" t="n">
-        <v>56692</v>
+        <v>56703</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,20 +957,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614390</v>
+        <v>614543</v>
       </c>
       <c r="R4" t="n">
-        <v>6942878</v>
+        <v>6942796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_348</t>
+          <t>2024_349</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>spillning i myrkant.</t>
+          <t>orrspillning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321598</v>
+        <v>123321603</v>
       </c>
       <c r="B5" t="n">
-        <v>56703</v>
+        <v>97996</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,21 +1096,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102613</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1118,9 +1118,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614543</v>
+        <v>614270</v>
       </c>
       <c r="R5" t="n">
-        <v>6942796</v>
+        <v>6942929</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_349</t>
+          <t>2024_344</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>orrspillning.</t>
+          <t>på myr</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Felix Gunnarsson, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321602</v>
+        <v>123321598</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>56703</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,35 +822,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614303</v>
+        <v>614543</v>
       </c>
       <c r="R3" t="n">
-        <v>6942906</v>
+        <v>6942796</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_345</t>
+          <t>2024_349</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>orrspillning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321598</v>
+        <v>123321602</v>
       </c>
       <c r="B4" t="n">
-        <v>56703</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,35 +957,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614543</v>
+        <v>614303</v>
       </c>
       <c r="R4" t="n">
-        <v>6942796</v>
+        <v>6942906</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_349</t>
+          <t>2024_345</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>orrspillning.</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321599</v>
+        <v>123321603</v>
       </c>
       <c r="B2" t="n">
-        <v>56692</v>
+        <v>97996</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614390</v>
+        <v>614270</v>
       </c>
       <c r="R2" t="n">
-        <v>6942878</v>
+        <v>6942929</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_348</t>
+          <t>2024_344</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>spillning i myrkant.</t>
+          <t>på myr</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
+          <t>Felix Gunnarsson, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321603</v>
+        <v>123321599</v>
       </c>
       <c r="B5" t="n">
-        <v>97996</v>
+        <v>56692</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,25 +1092,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1118,9 +1118,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614270</v>
+        <v>614390</v>
       </c>
       <c r="R5" t="n">
-        <v>6942929</v>
+        <v>6942878</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_344</t>
+          <t>2024_348</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>på myr</t>
+          <t>spillning i myrkant.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Douglas Skarp</t>
+          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321603</v>
+        <v>123321598</v>
       </c>
       <c r="B2" t="n">
-        <v>97996</v>
+        <v>56703</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,9 +713,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614270</v>
+        <v>614543</v>
       </c>
       <c r="R2" t="n">
-        <v>6942929</v>
+        <v>6942796</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_344</t>
+          <t>2024_349</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>på myr</t>
+          <t>orrspillning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Douglas Skarp</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123321598</v>
+        <v>123321599</v>
       </c>
       <c r="B3" t="n">
-        <v>56703</v>
+        <v>56692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,20 +822,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614543</v>
+        <v>614390</v>
       </c>
       <c r="R3" t="n">
-        <v>6942796</v>
+        <v>6942878</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_349</t>
+          <t>2024_348</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,12 +909,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>orrspillning.</t>
+          <t>spillning i myrkant.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,7 +934,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -945,10 +945,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321602</v>
+        <v>123321603</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>97996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -957,35 +957,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614303</v>
+        <v>614270</v>
       </c>
       <c r="R4" t="n">
-        <v>6942906</v>
+        <v>6942929</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_345</t>
+          <t>2024_344</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på gran</t>
+          <t>på myr</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Felix Gunnarsson, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1080,10 +1080,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321599</v>
+        <v>123321602</v>
       </c>
       <c r="B5" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,31 +1096,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614390</v>
+        <v>614303</v>
       </c>
       <c r="R5" t="n">
-        <v>6942878</v>
+        <v>6942906</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_348</t>
+          <t>2024_345</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1179,12 +1179,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>spillning i myrkant.</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Pattranit Kwanruen, Linnéa Kjellberg</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -675,47 +675,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123321598</v>
+        <v>123321602</v>
       </c>
       <c r="B2" t="n">
-        <v>56703</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614543</v>
+        <v>614303</v>
       </c>
       <c r="R2" t="n">
-        <v>6942796</v>
+        <v>6942906</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_349</t>
+          <t>2024_345</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>orrspillning.</t>
+          <t>på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnéa Kjellberg</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -813,16 +808,11 @@
         <v>123321599</v>
       </c>
       <c r="B3" t="n">
-        <v>56692</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -945,15 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123321603</v>
+        <v>123321598</v>
       </c>
       <c r="B4" t="n">
-        <v>97996</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -983,9 +968,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -994,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614270</v>
+        <v>614543</v>
       </c>
       <c r="R4" t="n">
-        <v>6942929</v>
+        <v>6942796</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_344</t>
+          <t>2024_349</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1034,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1044,12 +1029,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>på myr</t>
+          <t>orrspillning.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson, Douglas Skarp</t>
+          <t>Linnéa Kjellberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1080,15 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123321602</v>
+        <v>130669682</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,43 +1076,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flaggberget, Mpd</t>
+          <t>Holmmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614303</v>
+        <v>614481</v>
       </c>
       <c r="R5" t="n">
-        <v>6942906</v>
+        <v>6942834</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,7 +1139,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_345</t>
+          <t>568</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1167,24 +1147,9 @@
           <t>2024-05-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-05-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1199,12 +1164,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Isaksson</t>
+          <t>Alexander Hoffmann</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Alexander Hoffmann, Liam Martin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1215,32 +1180,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130669682</v>
+        <v>123321603</v>
       </c>
       <c r="B6" t="n">
-        <v>58316</v>
+        <v>99035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1248,21 +1213,21 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Holmmyrbäcken, Mpd</t>
+          <t>Flaggberget, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614481</v>
+        <v>614270</v>
       </c>
       <c r="R6" t="n">
-        <v>6942834</v>
+        <v>6942929</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,7 +1254,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>2024_344</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1297,9 +1262,24 @@
           <t>2024-05-21</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-05-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>på myr</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,12 +1294,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann</t>
+          <t>David Isaksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Hoffmann, Liam Martin</t>
+          <t>Felix Gunnarsson, Douglas Skarp</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">

--- a/artfynd/A 18829-2023 artfynd.xlsx
+++ b/artfynd/A 18829-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321602</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321599</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,6 +1077,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321598</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1177,6 +1197,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130669682</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1307,8 +1332,20 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123321603</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>